--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449626.7970662787</v>
+        <v>449627</v>
       </c>
       <c r="R2" t="n">
-        <v>6332463.866291232</v>
+        <v>6332464</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253763</v>
       </c>
       <c r="B2" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74253763</v>
+        <v>125662222</v>
       </c>
       <c r="B2" t="n">
-        <v>99346</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222322</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vika 200 m S om södra gården, Sm</t>
+          <t>Sjövik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449627</v>
+        <v>449643</v>
       </c>
       <c r="R2" t="n">
-        <v>6332464</v>
+        <v>6332348</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5E7a 0208. SOM: Carex hostiana. LEG: Lennart Persson, Evert Norell. KOM: Det. ThK</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,23 +779,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kärr i betesmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mats Johansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mats Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74253763</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99802</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vika 200 m S om södra gården, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>449627</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6332464</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Voxtorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5E7a 0208. SOM: Carex hostiana. LEG: Lennart Persson, Evert Norell. KOM: Det. ThK</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kärr i betesmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 53585-2022 artfynd.xlsx
+++ b/artfynd/A 53585-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125662222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,8 +912,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74253763</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>